--- a/delivery/paid-products/asgari-ucret-zam-etkisi-fiyat-ayarlama-cetveli/current.xlsx
+++ b/delivery/paid-products/asgari-ucret-zam-etkisi-fiyat-ayarlama-cetveli/current.xlsx
@@ -1477,6 +1477,270 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="A12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
     <comment ref="B6" authorId="0">
       <text>
         <r>
@@ -1668,6 +1932,270 @@
                 <xdr:colOff>103</xdr:colOff>
                 <xdr:row>7</xdr:row>
                 <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1873,6 +2401,270 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="C12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
     <comment ref="D6" authorId="0">
       <text>
         <r>
@@ -2064,6 +2856,270 @@
                 <xdr:colOff>103</xdr:colOff>
                 <xdr:row>7</xdr:row>
                 <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2269,6 +3325,270 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="E12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="E19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>83</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -2411,6 +3731,204 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="A10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="A15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
     <comment ref="B6" authorId="0">
       <text>
         <r>
@@ -2536,6 +4054,204 @@
                 <xdr:colOff>59</xdr:colOff>
                 <xdr:row>7</xdr:row>
                 <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="B15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -2675,6 +4391,204 @@
         <mc:Fallback/>
       </mc:AlternateContent>
     </comment>
+    <comment ref="C10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="C15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
     <comment ref="D6" authorId="0">
       <text>
         <r>
@@ -2800,6 +4714,204 @@
                 <xdr:colOff>59</xdr:colOff>
                 <xdr:row>7</xdr:row>
                 <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="D15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Tanım: Bu alan manuel veri girişi içindir | Neden önemli: Girilen değer hesaplamaları doğrudan etkiler | Doğru giriş: İstenen türde değer girin | Örnek: Tablo başlığına bakın | Yanlışsa: Sonuçlar yanlış hesaplanır</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>0</xdr:col>
+                <xdr:colOff>79</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>39</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>18</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3925,13 +6037,13 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>79</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>16</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
-                <xdr:row>8</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3958,13 +6070,13 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>79</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>16</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
-                <xdr:row>8</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -3991,13 +6103,13 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>79</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>16</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
-                <xdr:row>8</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4024,13 +6136,13 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>79</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>16</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
-                <xdr:row>8</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>2</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4057,13 +6169,13 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>79</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:rowOff>30</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
                 <xdr:row>9</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>16</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4090,13 +6202,13 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>79</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:rowOff>30</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
                 <xdr:row>9</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>16</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4123,13 +6235,13 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>79</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:rowOff>30</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
                 <xdr:row>9</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>16</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4156,13 +6268,13 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>79</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:rowOff>30</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
                 <xdr:row>9</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>16</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4189,13 +6301,13 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>79</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:rowOff>30</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
                 <xdr:row>9</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>16</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4222,13 +6334,13 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>79</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:rowOff>30</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
                 <xdr:row>9</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>16</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4255,13 +6367,13 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>79</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:rowOff>30</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
                 <xdr:row>9</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>16</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4288,13 +6400,13 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>79</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:rowOff>30</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
                 <xdr:row>9</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>16</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4321,13 +6433,13 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>79</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:rowOff>30</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
                 <xdr:row>9</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>16</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4354,13 +6466,13 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>79</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:rowOff>30</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
                 <xdr:row>9</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>16</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4387,13 +6499,13 @@
                 <xdr:col>0</xdr:col>
                 <xdr:colOff>79</xdr:colOff>
                 <xdr:row>0</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:rowOff>30</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>59</xdr:colOff>
                 <xdr:row>9</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:rowOff>16</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -4789,7 +6901,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="378">
   <si>
     <t xml:space="preserve">ASGARİ ÜCRET ZAM ETKİSİ &amp; FİYAT AYARLAMA CETVELİ</t>
   </si>
@@ -4950,6 +7062,54 @@
     <t xml:space="preserve">01.01.2021</t>
   </si>
   <si>
+    <t xml:space="preserve">Hasan Aydın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.03.2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elif Yıldız</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.07.2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murat Çetin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.11.2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selin Korkmaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.02.2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burak Koç</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.05.2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hatice Arslan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.08.2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emre Doğan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.12.2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nur Ateş</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01.10.2014</t>
+  </si>
+  <si>
     <t xml:space="preserve">Zam öncesi/sonrası maliyetler AYARLAR'daki oranlarla hesaplanır; veri girişi yalnızca sarı hücreleredir.</t>
   </si>
   <si>
@@ -4999,6 +7159,24 @@
   </si>
   <si>
     <t xml:space="preserve">İskele Kurulumu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duvar Örme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sıva İşleri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mermer Kaplama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Çatı Yalıtımı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boyacılık</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asmolen Döşeme</t>
   </si>
   <si>
     <t xml:space="preserve">İşçilik oranı birim maliyetin fiyattaki payıdır; yansıtma oranı bu payla çarpılır.</t>
@@ -6716,13 +8894,13 @@
                 <c:formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>153125</c:v>
+                  <c:v>387100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>162814.75</c:v>
+                  <c:v>436492</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3113.37599999999</c:v>
+                  <c:v>12584.6886075949</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6730,11 +8908,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="45190916"/>
-        <c:axId val="8656352"/>
+        <c:axId val="80263376"/>
+        <c:axId val="45329667"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="45190916"/>
+        <c:axId val="80263376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6767,7 +8945,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8656352"/>
+        <c:crossAx val="45329667"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -6775,7 +8953,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="8656352"/>
+        <c:axId val="45329667"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6818,7 +8996,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45190916"/>
+        <c:crossAx val="80263376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7017,10 +9195,10 @@
                 <c:formatCode>0.0%;[RED]\(0.0%\);\-</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.263624338624339</c:v>
+                  <c:v>0.332050518699942</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.736375661375661</c:v>
+                  <c:v>0.667949481300058</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7132,7 +9310,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1,6%</c:v>
+                  <c:v>3,2%</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7208,13 +9386,13 @@
                 <c:formatCode>0.0%;[RED]\(0.0%\);\-</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.0175777777777778</c:v>
+                  <c:v>0.0354430379746835</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0168746666666667</c:v>
+                  <c:v>0.0340253164556962</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.016272</c:v>
+                  <c:v>0.0328101265822785</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7222,11 +9400,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="4010955"/>
-        <c:axId val="19857656"/>
+        <c:axId val="32775032"/>
+        <c:axId val="5117052"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="4010955"/>
+        <c:axId val="32775032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7259,7 +9437,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19857656"/>
+        <c:crossAx val="5117052"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7267,7 +9445,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="19857656"/>
+        <c:axId val="5117052"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7310,7 +9488,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4010955"/>
+        <c:crossAx val="32775032"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7455,13 +9633,13 @@
                 <c:formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>9689.75</c:v>
+                  <c:v>49392</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3113.37599999999</c:v>
+                  <c:v>12584.6886075949</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6576.37400000001</c:v>
+                  <c:v>36807.3113924051</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7469,11 +9647,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="20746154"/>
-        <c:axId val="46639660"/>
+        <c:axId val="78416560"/>
+        <c:axId val="77628858"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="20746154"/>
+        <c:axId val="78416560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7506,7 +9684,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46639660"/>
+        <c:crossAx val="77628858"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7514,7 +9692,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46639660"/>
+        <c:axId val="77628858"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7557,7 +9735,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20746154"/>
+        <c:crossAx val="78416560"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7730,11 +9908,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="213138"/>
-        <c:axId val="59876679"/>
+        <c:axId val="64867231"/>
+        <c:axId val="25524623"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="213138"/>
+        <c:axId val="64867231"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7767,7 +9945,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59876679"/>
+        <c:crossAx val="25524623"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -7775,7 +9953,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59876679"/>
+        <c:axId val="25524623"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7818,7 +9996,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="213138"/>
+        <c:crossAx val="64867231"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7960,10 +10138,10 @@
                 <c:formatCode>"₺ "#,##0;[RED]"(₺ "#,##0\);\-</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>-3034.07317356957</c:v>
+                  <c:v>-900.974297101578</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>41496.875</c:v>
+                  <c:v>55951.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7971,11 +10149,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="16162004"/>
-        <c:axId val="25287642"/>
+        <c:axId val="27640958"/>
+        <c:axId val="75339836"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="16162004"/>
+        <c:axId val="27640958"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8008,7 +10186,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25287642"/>
+        <c:crossAx val="75339836"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -8016,7 +10194,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="25287642"/>
+        <c:axId val="75339836"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8059,7 +10237,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16162004"/>
+        <c:crossAx val="27640958"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9981,7 +12159,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -10025,12 +12203,12 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="31" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="B4" s="30" t="str">
         <f aca="false">firmaUnvani</f>
@@ -10039,16 +12217,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="31" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="B5" s="50" t="n">
         <f aca="false">raporTarihi</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="51" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="B6" s="52" t="str">
         <f aca="false">KararSonuc</f>
@@ -10057,16 +12235,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="B9" s="27" t="n">
         <f aca="false">ToplamMaliyetArtis</f>
-        <v>9689.75</v>
+        <v>49392</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10075,12 +12253,12 @@
       </c>
       <c r="B10" s="28" t="n">
         <f aca="false">MaliyetArtisOrani</f>
-        <v>0.06328</v>
+        <v>0.127594936708861</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="B11" s="28" t="n">
         <f aca="false">AsgariUcretZamOrani</f>
@@ -10089,53 +12267,53 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B12" s="28" t="n">
         <f aca="false">FiyatYansitmaOrani</f>
-        <v>0.0166821481481481</v>
+        <v>0.0423679649176635</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="B13" s="27" t="n">
         <f aca="false">FiyatYansitmaKazanci</f>
-        <v>3113.37599999999</v>
+        <v>12584.6886075949</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="B14" s="27" t="n">
         <f aca="false">modulI7AcikKopru</f>
-        <v>6576.37400000001</v>
+        <v>36807.3113924051</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="B15" s="26" t="n">
         <f aca="false">VeriKaliteSkoru</f>
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B16" s="26" t="n">
         <f aca="false">ToplamCalisanSayisi</f>
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="53" t="str">
         <f aca="false">KararGerekce</f>
-        <v>Fiyat yansıtması maliyet artışını karşılamıyor; açık 6.576 ₺.</v>
+        <v>Fiyat yansıtması maliyet artışını karşılamıyor; açık 36.807 ₺.</v>
       </c>
       <c r="B18" s="53"/>
       <c r="C18" s="53"/>
@@ -10147,85 +12325,85 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="24" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="24" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="24" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="36" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="B31" s="36"/>
       <c r="C31" s="36"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="36" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="B32" s="36"/>
       <c r="C32" s="36"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="36" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="B33" s="36"/>
       <c r="C33" s="36"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="7"/>
@@ -10235,7 +12413,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -10312,7 +12490,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -10346,7 +12524,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10470,27 +12648,27 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="E16" s="15"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="54" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="B17" s="47" t="n">
         <v>1200</v>
@@ -10504,7 +12682,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="54" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B18" s="47" t="n">
         <v>900</v>
@@ -10518,7 +12696,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="54" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B19" s="47" t="n">
         <v>1500</v>
@@ -10532,7 +12710,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="54" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="B20" s="47" t="n">
         <v>700</v>
@@ -10546,7 +12724,7 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -10619,7 +12797,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -10653,29 +12831,29 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="54" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -10706,7 +12884,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -10740,12 +12918,12 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10760,12 +12938,12 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="55" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="B11" s="11"/>
       <c r="C11" s="11"/>
@@ -10843,7 +13021,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -10877,7 +13055,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
@@ -10889,7 +13067,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -10901,840 +13079,840 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="56" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="C6" s="57" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="F6" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="G6" s="59" t="s">
         <v>251</v>
       </c>
-      <c r="G6" s="59" t="s">
-        <v>229</v>
-      </c>
       <c r="H6" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="56" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="C7" s="60" t="n">
         <f aca="true">TODAY()</f>
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="E7" s="58" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="F7" s="58" t="s">
+        <v>273</v>
+      </c>
+      <c r="G7" s="59" t="s">
         <v>251</v>
       </c>
-      <c r="G7" s="59" t="s">
-        <v>229</v>
-      </c>
       <c r="H7" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="56" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="C8" s="61" t="n">
         <v>12000</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="E8" s="58" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="56" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="C9" s="61" t="n">
         <v>15000</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="E9" s="58" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="F9" s="58" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="G9" s="59" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="H9" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="56" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="C10" s="62" t="n">
         <v>0.205</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E10" s="58" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="H10" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="56" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="B11" s="56" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="C11" s="62" t="n">
         <v>0.02</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E11" s="58" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="G11" s="59" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="H11" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="56" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="B12" s="56" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="C12" s="62" t="n">
         <v>0.14</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="G12" s="59" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="H12" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="56" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="B13" s="56" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="C13" s="62" t="n">
         <v>0.01</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E13" s="58" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="F13" s="58" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="G13" s="59" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="H13" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="56" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="B14" s="56" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="C14" s="63" t="n">
         <v>30</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="E14" s="58" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="G14" s="59" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="H14" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="56" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="B15" s="56" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="C15" s="63" t="n">
         <v>8</v>
       </c>
       <c r="D15" s="56" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="E15" s="58" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="F15" s="58" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="G15" s="59" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="H15" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="56" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="B16" s="56" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="C16" s="62" t="n">
         <v>1E-007</v>
       </c>
       <c r="D16" s="56" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G16" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H16" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="56" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="B17" s="56" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="C17" s="62" t="n">
         <v>0.1</v>
       </c>
       <c r="D17" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E17" s="58" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="F17" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G17" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H17" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="56" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="B18" s="56" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="C18" s="62" t="n">
         <v>0.15</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E18" s="58" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="F18" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G18" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H18" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="56" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="B19" s="56" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="C19" s="63" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E19" s="58" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="F19" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G19" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H19" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="56" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="B20" s="56" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="C20" s="63" t="n">
         <v>90</v>
       </c>
       <c r="D20" s="56" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G20" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H20" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="56" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="B21" s="56" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="C21" s="63" t="n">
         <v>70</v>
       </c>
       <c r="D21" s="56" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="E21" s="58" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="F21" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G21" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H21" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="56" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="B22" s="56" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="C22" s="63" t="n">
         <v>10</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="E22" s="58" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="F22" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G22" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H22" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="56" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="B23" s="56" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="C23" s="62" t="n">
         <v>0.1</v>
       </c>
       <c r="D23" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E23" s="58" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="F23" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G23" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H23" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="56" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="B24" s="56" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="C24" s="62" t="n">
         <v>0.1</v>
       </c>
       <c r="D24" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E24" s="58" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="F24" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G24" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H24" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="56" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="C25" s="62" t="n">
         <v>0.05</v>
       </c>
       <c r="D25" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E25" s="58" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="F25" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G25" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H25" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="56" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="B26" s="56" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="C26" s="62" t="n">
         <v>0.3</v>
       </c>
       <c r="D26" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E26" s="58" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="F26" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G26" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H26" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="56" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="B27" s="56" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="C27" s="62" t="n">
         <v>0.9</v>
       </c>
       <c r="D27" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E27" s="58" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="F27" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G27" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H27" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="56" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="C28" s="62" t="n">
         <v>0.1</v>
       </c>
       <c r="D28" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E28" s="58" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="F28" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G28" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H28" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="56" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="B29" s="56" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="C29" s="63" t="n">
         <v>1800</v>
       </c>
       <c r="D29" s="56" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="E29" s="58" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="F29" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G29" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H29" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="56" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="B30" s="56" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="C30" s="63" t="n">
         <v>100</v>
       </c>
       <c r="D30" s="56" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="E30" s="58" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="F30" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G30" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H30" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="56" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="C31" s="63" t="n">
         <v>20</v>
       </c>
       <c r="D31" s="56" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="E31" s="58" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="F31" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G31" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H31" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="56" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="B32" s="56" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C32" s="63" t="n">
         <v>3000</v>
       </c>
       <c r="D32" s="56" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="E32" s="58" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="F32" s="58" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="G32" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H32" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="56" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="C33" s="62" t="n">
         <v>0.6</v>
       </c>
       <c r="D33" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E33" s="58" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="F33" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G33" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H33" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="56" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="B34" s="56" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="C34" s="62" t="n">
         <v>0.1</v>
       </c>
       <c r="D34" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E34" s="58" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="F34" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G34" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H34" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="56" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="C35" s="62" t="n">
         <v>0.5</v>
       </c>
       <c r="D35" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E35" s="58" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="F35" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G35" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H35" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="56" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="C36" s="62" t="n">
         <v>0.5</v>
       </c>
       <c r="D36" s="56" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="E36" s="58" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="F36" s="58" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="G36" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="H36" s="59" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -11808,7 +13986,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -11842,12 +14020,12 @@
     </row>
     <row r="3" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -11911,7 +14089,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -11975,7 +14153,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -12039,7 +14217,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -12103,7 +14281,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -12167,7 +14345,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -12231,7 +14409,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -12295,7 +14473,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -12359,7 +14537,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -12423,7 +14601,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -12487,7 +14665,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -12551,7 +14729,7 @@
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -13396,7 +15574,7 @@
       </c>
       <c r="L6" s="0" t="n">
         <f aca="false">IF(OR($B6=""),"",IFERROR(MAX(0,DATEDIF($B6,raporTarihi,"D")),0))</f>
-        <v>2352</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13441,7 +15619,7 @@
       </c>
       <c r="L7" s="0" t="n">
         <f aca="false">IF(OR($B7=""),"",IFERROR(MAX(0,DATEDIF($B7,raporTarihi,"D")),0))</f>
-        <v>4087</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13486,7 +15664,7 @@
       </c>
       <c r="L8" s="0" t="n">
         <f aca="false">IF(OR($B8=""),"",IFERROR(MAX(0,DATEDIF($B8,raporTarihi,"D")),0))</f>
-        <v>1667</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13531,7 +15709,7 @@
       </c>
       <c r="L9" s="0" t="n">
         <f aca="false">IF(OR($B9=""),"",IFERROR(MAX(0,DATEDIF($B9,raporTarihi,"D")),0))</f>
-        <v>3052</v>
+        <v>3053</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13576,7 +15754,7 @@
       </c>
       <c r="L10" s="0" t="n">
         <f aca="false">IF(OR($B10=""),"",IFERROR(MAX(0,DATEDIF($B10,raporTarihi,"D")),0))</f>
-        <v>2534</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13621,64 +15799,368 @@
       </c>
       <c r="L11" s="0" t="n">
         <f aca="false">IF(OR($B11=""),"",IFERROR(MAX(0,DATEDIF($B11,raporTarihi,"D")),0))</f>
-        <v>2046</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
+      <c r="A12" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>16000</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <f aca="false">IF(OR($C12="",$D12=""),"",IFERROR($C12/(UcretHesaplamaGun*GunlukCalismaSaat),0))</f>
+        <v>66.6666666666667</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <f aca="false">IF(OR($C12="",$D12=""),"",IF($D12="Asgari",AsgariUcretYeni,IF($D12="Ust Oran",$C12*(1+IF($E12="",0,$E12)),$C12)))</f>
+        <v>15000</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <f aca="false">IF(OR($C12="",$D12=""),"",IFERROR($C12*(1+SgkIsverenOran+IssizlikIsverenOran),0))</f>
+        <v>19600</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <f aca="false">IF(OR($C12="",$D12=""),"",IFERROR($G12*(1+SgkIsverenOran+IssizlikIsverenOran),0))</f>
+        <v>18375</v>
+      </c>
+      <c r="J12" s="0" t="n">
+        <f aca="false">IF(OR($H12="",$I12=""),"",IFERROR($I12-$H12,0))</f>
+        <v>-1225</v>
+      </c>
+      <c r="K12" s="0" t="n">
+        <f aca="false">IF(OR($J12="",$H12=""),"",IFERROR($J12/MAX(BolumPaydaTaban,$H12),0))</f>
+        <v>-0.0625</v>
+      </c>
+      <c r="L12" s="0" t="n">
+        <f aca="false">IF(OR($B12=""),"",IFERROR(MAX(0,DATEDIF($B12,raporTarihi,"D")),0))</f>
+        <v>1258</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
+      <c r="A13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <f aca="false">IF(OR($C13="",$D13=""),"",IFERROR($C13/(UcretHesaplamaGun*GunlukCalismaSaat),0))</f>
+        <v>125</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <f aca="false">IF(OR($C13="",$D13=""),"",IF($D13="Asgari",AsgariUcretYeni,IF($D13="Ust Oran",$C13*(1+IF($E13="",0,$E13)),$C13)))</f>
+        <v>35400</v>
+      </c>
+      <c r="H13" s="0" t="n">
+        <f aca="false">IF(OR($C13="",$D13=""),"",IFERROR($C13*(1+SgkIsverenOran+IssizlikIsverenOran),0))</f>
+        <v>36750</v>
+      </c>
+      <c r="I13" s="0" t="n">
+        <f aca="false">IF(OR($C13="",$D13=""),"",IFERROR($G13*(1+SgkIsverenOran+IssizlikIsverenOran),0))</f>
+        <v>43365</v>
+      </c>
+      <c r="J13" s="0" t="n">
+        <f aca="false">IF(OR($H13="",$I13=""),"",IFERROR($I13-$H13,0))</f>
+        <v>6615</v>
+      </c>
+      <c r="K13" s="0" t="n">
+        <f aca="false">IF(OR($J13="",$H13=""),"",IFERROR($J13/MAX(BolumPaydaTaban,$H13),0))</f>
+        <v>0.18</v>
+      </c>
+      <c r="L13" s="0" t="n">
+        <f aca="false">IF(OR($B13=""),"",IFERROR(MAX(0,DATEDIF($B13,raporTarihi,"D")),0))</f>
+        <v>3327</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
+      <c r="A14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>14000</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="0" t="n">
+        <f aca="false">IF(OR($C14="",$D14=""),"",IFERROR($C14/(UcretHesaplamaGun*GunlukCalismaSaat),0))</f>
+        <v>58.3333333333333</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <f aca="false">IF(OR($C14="",$D14=""),"",IF($D14="Asgari",AsgariUcretYeni,IF($D14="Ust Oran",$C14*(1+IF($E14="",0,$E14)),$C14)))</f>
+        <v>15000</v>
+      </c>
+      <c r="H14" s="0" t="n">
+        <f aca="false">IF(OR($C14="",$D14=""),"",IFERROR($C14*(1+SgkIsverenOran+IssizlikIsverenOran),0))</f>
+        <v>17150</v>
+      </c>
+      <c r="I14" s="0" t="n">
+        <f aca="false">IF(OR($C14="",$D14=""),"",IFERROR($G14*(1+SgkIsverenOran+IssizlikIsverenOran),0))</f>
+        <v>18375</v>
+      </c>
+      <c r="J14" s="0" t="n">
+        <f aca="false">IF(OR($H14="",$I14=""),"",IFERROR($I14-$H14,0))</f>
+        <v>1225</v>
+      </c>
+      <c r="K14" s="0" t="n">
+        <f aca="false">IF(OR($J14="",$H14=""),"",IFERROR($J14/MAX(BolumPaydaTaban,$H14),0))</f>
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="L14" s="0" t="n">
+        <f aca="false">IF(OR($B14=""),"",IFERROR(MAX(0,DATEDIF($B14,raporTarihi,"D")),0))</f>
+        <v>2108</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
+      <c r="A15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>22000</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F15" s="0" t="n">
+        <f aca="false">IF(OR($C15="",$D15=""),"",IFERROR($C15/(UcretHesaplamaGun*GunlukCalismaSaat),0))</f>
+        <v>91.6666666666667</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <f aca="false">IF(OR($C15="",$D15=""),"",IF($D15="Asgari",AsgariUcretYeni,IF($D15="Ust Oran",$C15*(1+IF($E15="",0,$E15)),$C15)))</f>
+        <v>23760</v>
+      </c>
+      <c r="H15" s="0" t="n">
+        <f aca="false">IF(OR($C15="",$D15=""),"",IFERROR($C15*(1+SgkIsverenOran+IssizlikIsverenOran),0))</f>
+        <v>26950</v>
+      </c>
+      <c r="I15" s="0" t="n">
+        <f aca="false">IF(OR($C15="",$D15=""),"",IFERROR($G15*(1+SgkIsverenOran+IssizlikIsverenOran),0))</f>
+        <v>29106</v>
+      </c>
+      <c r="J15" s="0" t="n">
+        <f aca="false">IF(OR($H15="",$I15=""),"",IFERROR($I15-$H15,0))</f>
+        <v>2156</v>
+      </c>
+      <c r="K15" s="0" t="n">
+        <f aca="false">IF(OR($J15="",$H15=""),"",IFERROR($J15/MAX(BolumPaydaTaban,$H15),0))</f>
+        <v>0.08</v>
+      </c>
+      <c r="L15" s="0" t="n">
+        <f aca="false">IF(OR($B15=""),"",IFERROR(MAX(0,DATEDIF($B15,raporTarihi,"D")),0))</f>
+        <v>2747</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
+      <c r="A16" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <f aca="false">IF(OR($C16="",$D16=""),"",IFERROR($C16/(UcretHesaplamaGun*GunlukCalismaSaat),0))</f>
+        <v>54.1666666666667</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <f aca="false">IF(OR($C16="",$D16=""),"",IF($D16="Asgari",AsgariUcretYeni,IF($D16="Ust Oran",$C16*(1+IF($E16="",0,$E16)),$C16)))</f>
+        <v>15000</v>
+      </c>
+      <c r="H16" s="0" t="n">
+        <f aca="false">IF(OR($C16="",$D16=""),"",IFERROR($C16*(1+SgkIsverenOran+IssizlikIsverenOran),0))</f>
+        <v>15925</v>
+      </c>
+      <c r="I16" s="0" t="n">
+        <f aca="false">IF(OR($C16="",$D16=""),"",IFERROR($G16*(1+SgkIsverenOran+IssizlikIsverenOran),0))</f>
+        <v>18375</v>
+      </c>
+      <c r="J16" s="0" t="n">
+        <f aca="false">IF(OR($H16="",$I16=""),"",IFERROR($I16-$H16,0))</f>
+        <v>2450</v>
+      </c>
+      <c r="K16" s="0" t="n">
+        <f aca="false">IF(OR($J16="",$H16=""),"",IFERROR($J16/MAX(BolumPaydaTaban,$H16),0))</f>
+        <v>0.153846153846154</v>
+      </c>
+      <c r="L16" s="0" t="n">
+        <f aca="false">IF(OR($B16=""),"",IFERROR(MAX(0,DATEDIF($B16,raporTarihi,"D")),0))</f>
+        <v>831</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
+      <c r="A17" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <f aca="false">IF(OR($C17="",$D17=""),"",IFERROR($C17/(UcretHesaplamaGun*GunlukCalismaSaat),0))</f>
+        <v>166.666666666667</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <f aca="false">IF(OR($C17="",$D17=""),"",IF($D17="Asgari",AsgariUcretYeni,IF($D17="Ust Oran",$C17*(1+IF($E17="",0,$E17)),$C17)))</f>
+        <v>48000</v>
+      </c>
+      <c r="H17" s="0" t="n">
+        <f aca="false">IF(OR($C17="",$D17=""),"",IFERROR($C17*(1+SgkIsverenOran+IssizlikIsverenOran),0))</f>
+        <v>49000</v>
+      </c>
+      <c r="I17" s="0" t="n">
+        <f aca="false">IF(OR($C17="",$D17=""),"",IFERROR($G17*(1+SgkIsverenOran+IssizlikIsverenOran),0))</f>
+        <v>58800</v>
+      </c>
+      <c r="J17" s="0" t="n">
+        <f aca="false">IF(OR($H17="",$I17=""),"",IFERROR($I17-$H17,0))</f>
+        <v>9800.00000000001</v>
+      </c>
+      <c r="K17" s="0" t="n">
+        <f aca="false">IF(OR($J17="",$H17=""),"",IFERROR($J17/MAX(BolumPaydaTaban,$H17),0))</f>
+        <v>0.2</v>
+      </c>
+      <c r="L17" s="0" t="n">
+        <f aca="false">IF(OR($B17=""),"",IFERROR(MAX(0,DATEDIF($B17,raporTarihi,"D")),0))</f>
+        <v>3661</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
+      <c r="A18" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>11000</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <f aca="false">IF(OR($C18="",$D18=""),"",IFERROR($C18/(UcretHesaplamaGun*GunlukCalismaSaat),0))</f>
+        <v>45.8333333333333</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <f aca="false">IF(OR($C18="",$D18=""),"",IF($D18="Asgari",AsgariUcretYeni,IF($D18="Ust Oran",$C18*(1+IF($E18="",0,$E18)),$C18)))</f>
+        <v>15000</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <f aca="false">IF(OR($C18="",$D18=""),"",IFERROR($C18*(1+SgkIsverenOran+IssizlikIsverenOran),0))</f>
+        <v>13475</v>
+      </c>
+      <c r="I18" s="0" t="n">
+        <f aca="false">IF(OR($C18="",$D18=""),"",IFERROR($G18*(1+SgkIsverenOran+IssizlikIsverenOran),0))</f>
+        <v>18375</v>
+      </c>
+      <c r="J18" s="0" t="n">
+        <f aca="false">IF(OR($H18="",$I18=""),"",IFERROR($I18-$H18,0))</f>
+        <v>4900</v>
+      </c>
+      <c r="K18" s="0" t="n">
+        <f aca="false">IF(OR($J18="",$H18=""),"",IFERROR($J18/MAX(BolumPaydaTaban,$H18),0))</f>
+        <v>0.363636363636364</v>
+      </c>
+      <c r="L18" s="0" t="n">
+        <f aca="false">IF(OR($B18=""),"",IFERROR(MAX(0,DATEDIF($B18,raporTarihi,"D")),0))</f>
+        <v>1348</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
+      <c r="A19" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <f aca="false">IF(OR($C19="",$D19=""),"",IFERROR($C19/(UcretHesaplamaGun*GunlukCalismaSaat),0))</f>
+        <v>187.5</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <f aca="false">IF(OR($C19="",$D19=""),"",IF($D19="Asgari",AsgariUcretYeni,IF($D19="Ust Oran",$C19*(1+IF($E19="",0,$E19)),$C19)))</f>
+        <v>56250</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <f aca="false">IF(OR($C19="",$D19=""),"",IFERROR($C19*(1+SgkIsverenOran+IssizlikIsverenOran),0))</f>
+        <v>55125</v>
+      </c>
+      <c r="I19" s="0" t="n">
+        <f aca="false">IF(OR($C19="",$D19=""),"",IFERROR($G19*(1+SgkIsverenOran+IssizlikIsverenOran),0))</f>
+        <v>68906.25</v>
+      </c>
+      <c r="J19" s="0" t="n">
+        <f aca="false">IF(OR($H19="",$I19=""),"",IFERROR($I19-$H19,0))</f>
+        <v>13781.25</v>
+      </c>
+      <c r="K19" s="0" t="n">
+        <f aca="false">IF(OR($J19="",$H19=""),"",IFERROR($J19/MAX(BolumPaydaTaban,$H19),0))</f>
+        <v>0.25</v>
+      </c>
+      <c r="L19" s="0" t="n">
+        <f aca="false">IF(OR($B19=""),"",IFERROR(MAX(0,DATEDIF($B19,raporTarihi,"D")),0))</f>
+        <v>4331</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21"/>
@@ -20577,7 +23059,7 @@
     </row>
     <row r="1006" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1006" s="11" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B1006" s="11"/>
       <c r="C1006" s="11"/>
@@ -20692,7 +23174,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -20726,12 +23208,12 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -20744,36 +23226,36 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="B6" s="17" t="n">
         <v>1200</v>
@@ -20790,15 +23272,15 @@
       </c>
       <c r="F6" s="0" t="n">
         <f aca="false">IF(OR($E6="",MaliyetArtisOrani=""),"",IFERROR($E6*MaliyetArtisOrani,0))</f>
-        <v>0.01582</v>
+        <v>0.0318987341772152</v>
       </c>
       <c r="G6" s="0" t="n">
         <f aca="false">IF(OR($B6="",$F6=""),"",IFERROR($B6*(1+$F6),0))</f>
-        <v>1218.984</v>
+        <v>1238.27848101266</v>
       </c>
       <c r="H6" s="0" t="n">
         <f aca="false">IF(OR($G6="",$D6=""),"",IFERROR($G6*$D6,0))</f>
-        <v>60949.2</v>
+        <v>61913.9240506329</v>
       </c>
       <c r="I6" s="0" t="n">
         <f aca="false">IF(OR($C6="",$D6=""),"",IFERROR($C6*$D6,0))</f>
@@ -20807,7 +23289,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B7" s="17" t="n">
         <v>900</v>
@@ -20824,15 +23306,15 @@
       </c>
       <c r="F7" s="0" t="n">
         <f aca="false">IF(OR($E7="",MaliyetArtisOrani=""),"",IFERROR($E7*MaliyetArtisOrani,0))</f>
-        <v>0.0175777777777778</v>
+        <v>0.0354430379746835</v>
       </c>
       <c r="G7" s="0" t="n">
         <f aca="false">IF(OR($B7="",$F7=""),"",IFERROR($B7*(1+$F7),0))</f>
-        <v>915.82</v>
+        <v>931.898734177215</v>
       </c>
       <c r="H7" s="0" t="n">
         <f aca="false">IF(OR($G7="",$D7=""),"",IFERROR($G7*$D7,0))</f>
-        <v>54949.2</v>
+        <v>55913.9240506329</v>
       </c>
       <c r="I7" s="0" t="n">
         <f aca="false">IF(OR($C7="",$D7=""),"",IFERROR($C7*$D7,0))</f>
@@ -20841,7 +23323,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B8" s="17" t="n">
         <v>1500</v>
@@ -20858,15 +23340,15 @@
       </c>
       <c r="F8" s="0" t="n">
         <f aca="false">IF(OR($E8="",MaliyetArtisOrani=""),"",IFERROR($E8*MaliyetArtisOrani,0))</f>
-        <v>0.0168746666666667</v>
+        <v>0.0340253164556962</v>
       </c>
       <c r="G8" s="0" t="n">
         <f aca="false">IF(OR($B8="",$F8=""),"",IFERROR($B8*(1+$F8),0))</f>
-        <v>1525.312</v>
+        <v>1551.03797468354</v>
       </c>
       <c r="H8" s="0" t="n">
         <f aca="false">IF(OR($G8="",$D8=""),"",IFERROR($G8*$D8,0))</f>
-        <v>45759.36</v>
+        <v>46531.1392405063</v>
       </c>
       <c r="I8" s="0" t="n">
         <f aca="false">IF(OR($C8="",$D8=""),"",IFERROR($C8*$D8,0))</f>
@@ -20875,7 +23357,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="B9" s="17" t="n">
         <v>700</v>
@@ -20892,15 +23374,15 @@
       </c>
       <c r="F9" s="0" t="n">
         <f aca="false">IF(OR($E9="",MaliyetArtisOrani=""),"",IFERROR($E9*MaliyetArtisOrani,0))</f>
-        <v>0.016272</v>
+        <v>0.0328101265822785</v>
       </c>
       <c r="G9" s="0" t="n">
         <f aca="false">IF(OR($B9="",$F9=""),"",IFERROR($B9*(1+$F9),0))</f>
-        <v>711.3904</v>
+        <v>722.967088607595</v>
       </c>
       <c r="H9" s="0" t="n">
         <f aca="false">IF(OR($G9="",$D9=""),"",IFERROR($G9*$D9,0))</f>
-        <v>28455.616</v>
+        <v>28918.6835443038</v>
       </c>
       <c r="I9" s="0" t="n">
         <f aca="false">IF(OR($C9="",$D9=""),"",IFERROR($C9*$D9,0))</f>
@@ -20908,40 +23390,208 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
+      <c r="A10" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>850</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>220</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>45</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <f aca="false">IF(OR($B10="",$C10=""),"",IFERROR($C10/MAX(BolumPaydaTaban,$B10),0))</f>
+        <v>0.258823529411765</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <f aca="false">IF(OR($E10="",MaliyetArtisOrani=""),"",IFERROR($E10*MaliyetArtisOrani,0))</f>
+        <v>0.0330245718540581</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <f aca="false">IF(OR($B10="",$F10=""),"",IFERROR($B10*(1+$F10),0))</f>
+        <v>878.070886075949</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <f aca="false">IF(OR($G10="",$D10=""),"",IFERROR($G10*$D10,0))</f>
+        <v>39513.1898734177</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <f aca="false">IF(OR($C10="",$D10=""),"",IFERROR($C10*$D10,0))</f>
+        <v>9900</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
+      <c r="A11" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>190</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <f aca="false">IF(OR($B11="",$C11=""),"",IFERROR($C11/MAX(BolumPaydaTaban,$B11),0))</f>
+        <v>0.316666666666667</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <f aca="false">IF(OR($E11="",MaliyetArtisOrani=""),"",IFERROR($E11*MaliyetArtisOrani,0))</f>
+        <v>0.0404050632911392</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <f aca="false">IF(OR($B11="",$F11=""),"",IFERROR($B11*(1+$F11),0))</f>
+        <v>624.243037974684</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <f aca="false">IF(OR($G11="",$D11=""),"",IFERROR($G11*$D11,0))</f>
+        <v>21848.5063291139</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <f aca="false">IF(OR($C11="",$D11=""),"",IFERROR($C11*$D11,0))</f>
+        <v>6650</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
+      <c r="A12" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>350</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>420</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <f aca="false">IF(OR($B12="",$C12=""),"",IFERROR($C12/MAX(BolumPaydaTaban,$B12),0))</f>
+        <v>1.2</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <f aca="false">IF(OR($E12="",MaliyetArtisOrani=""),"",IFERROR($E12*MaliyetArtisOrani,0))</f>
+        <v>0.153113924050633</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <f aca="false">IF(OR($B12="",$F12=""),"",IFERROR($B12*(1+$F12),0))</f>
+        <v>403.589873417722</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <f aca="false">IF(OR($G12="",$D12=""),"",IFERROR($G12*$D12,0))</f>
+        <v>10089.746835443</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <f aca="false">IF(OR($C12="",$D12=""),"",IFERROR($C12*$D12,0))</f>
+        <v>10500</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
+      <c r="A13" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>420</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>280</v>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <f aca="false">IF(OR($B13="",$C13=""),"",IFERROR($C13/MAX(BolumPaydaTaban,$B13),0))</f>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <f aca="false">IF(OR($E13="",MaliyetArtisOrani=""),"",IFERROR($E13*MaliyetArtisOrani,0))</f>
+        <v>0.0850632911392405</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <f aca="false">IF(OR($B13="",$F13=""),"",IFERROR($B13*(1+$F13),0))</f>
+        <v>455.726582278481</v>
+      </c>
+      <c r="H13" s="0" t="n">
+        <f aca="false">IF(OR($G13="",$D13=""),"",IFERROR($G13*$D13,0))</f>
+        <v>9114.53164556962</v>
+      </c>
+      <c r="I13" s="0" t="n">
+        <f aca="false">IF(OR($C13="",$D13=""),"",IFERROR($C13*$D13,0))</f>
+        <v>5600</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
+      <c r="A14" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>160</v>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>55</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <f aca="false">IF(OR($B14="",$C14=""),"",IFERROR($C14/MAX(BolumPaydaTaban,$B14),0))</f>
+        <v>0.145454545454545</v>
+      </c>
+      <c r="F14" s="0" t="n">
+        <f aca="false">IF(OR($E14="",MaliyetArtisOrani=""),"",IFERROR($E14*MaliyetArtisOrani,0))</f>
+        <v>0.0185592635212888</v>
+      </c>
+      <c r="G14" s="0" t="n">
+        <f aca="false">IF(OR($B14="",$F14=""),"",IFERROR($B14*(1+$F14),0))</f>
+        <v>1120.41518987342</v>
+      </c>
+      <c r="H14" s="0" t="n">
+        <f aca="false">IF(OR($G14="",$D14=""),"",IFERROR($G14*$D14,0))</f>
+        <v>61622.835443038</v>
+      </c>
+      <c r="I14" s="0" t="n">
+        <f aca="false">IF(OR($C14="",$D14=""),"",IFERROR($C14*$D14,0))</f>
+        <v>8800</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
+      <c r="A15" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>750</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>210</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>38</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <f aca="false">IF(OR($B15="",$C15=""),"",IFERROR($C15/MAX(BolumPaydaTaban,$B15),0))</f>
+        <v>0.28</v>
+      </c>
+      <c r="F15" s="0" t="n">
+        <f aca="false">IF(OR($E15="",MaliyetArtisOrani=""),"",IFERROR($E15*MaliyetArtisOrani,0))</f>
+        <v>0.035726582278481</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <f aca="false">IF(OR($B15="",$F15=""),"",IFERROR($B15*(1+$F15),0))</f>
+        <v>776.794936708861</v>
+      </c>
+      <c r="H15" s="0" t="n">
+        <f aca="false">IF(OR($G15="",$D15=""),"",IFERROR($G15*$D15,0))</f>
+        <v>29518.2075949367</v>
+      </c>
+      <c r="I15" s="0" t="n">
+        <f aca="false">IF(OR($C15="",$D15=""),"",IFERROR($C15*$D15,0))</f>
+        <v>7980</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21"/>
@@ -32879,7 +35529,7 @@
     </row>
     <row r="2006" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2006" s="11" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="B2006" s="11"/>
       <c r="C2006" s="11"/>
@@ -32980,7 +35630,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -33014,48 +35664,48 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="B7" s="26" t="n">
         <f aca="false">IFERROR(COUNTA(tblCalisan[Çalışan Adı]),0)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="B8" s="27" t="n">
         <f aca="false">IFERROR(SUM(tblCalisan[Zam Öncesi Brüt Ücret (₺)]),0)</f>
-        <v>125000</v>
+        <v>316000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="B9" s="27" t="n">
         <f aca="false">IFERROR(SUM(tblCalisan[Zam Sonrası Brüt Ücret (₺)]),0)</f>
-        <v>132910</v>
+        <v>356320</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33064,7 +35714,7 @@
       </c>
       <c r="B10" s="27" t="n">
         <f aca="false">IFERROR(SUM(tblCalisan[Zam Öncesi İşveren Maliyeti (₺)]),0)</f>
-        <v>153125</v>
+        <v>387100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33073,16 +35723,16 @@
       </c>
       <c r="B11" s="27" t="n">
         <f aca="false">IFERROR(SUM(tblCalisan[Zam Sonrası İşveren Maliyeti (₺)]),0)</f>
-        <v>162814.75</v>
+        <v>436492</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="B12" s="27" t="n">
         <f aca="false">IFERROR(ZamSonrasiIsverenMaliyeti-ZamOncesiIsverenMaliyeti,0)</f>
-        <v>9689.75</v>
+        <v>49392</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33091,12 +35741,12 @@
       </c>
       <c r="B13" s="28" t="n">
         <f aca="false">IFERROR(ToplamMaliyetArtis/MAX(BolumPaydaTaban,ZamOncesiIsverenMaliyeti),0)</f>
-        <v>0.06328</v>
+        <v>0.127594936708861</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="B14" s="28" t="n">
         <f aca="false">IFERROR(IF(COUNTA(tblCalisan[Çalışan Adı])=0,0,(AsgariUcretYeni-AsgariUcretEski)/MAX(BolumPaydaTaban,AsgariUcretEski)),0)</f>
@@ -33105,250 +35755,250 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="B15" s="28" t="n">
         <f aca="false">IFERROR(AVERAGE(tblCalisan[Maliyet Artış Oranı]),0)</f>
-        <v>0.0616666666666667</v>
+        <v>0.114743649207935</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="B16" s="27" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(tblUrun[Önerilen Yeni Fiyat (₺)],tblUrun[Aylık Adet]),0)</f>
-        <v>190113.376</v>
+        <v>364984.688607595</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="B17" s="27" t="n">
         <f aca="false">IFERROR(SUM(tblUrun[Aylık İşçilik Yükü (₺)]),0)</f>
-        <v>49200</v>
+        <v>98630</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="B18" s="28" t="n">
         <f aca="false">IFERROR(IF(SUM(tblUrun[Aylık Adet])=0,0,SUMPRODUCT(tblUrun[Fiyat Yansıtma Oranı],tblUrun[Aylık Adet])/MAX(BolumPaydaTaban,SUM(tblUrun[Aylık Adet]))),0)</f>
-        <v>0.0166821481481481</v>
+        <v>0.0423679649176635</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="B19" s="27" t="n">
         <f aca="false">IFERROR(SUMPRODUCT(tblUrun[Önerilen Yeni Fiyat (₺)]-tblUrun[Birim Satış Fiyatı (₺)],tblUrun[Aylık Adet]),0)</f>
-        <v>3113.37599999999</v>
+        <v>12584.6886075949</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="B20" s="26" t="n">
         <f aca="false">IFERROR(COUNTIF(tblCalisan[Zam Öncesi Brüt Ücret (₺)],"&gt;"&amp;IFERROR(AVERAGE(tblCalisan[Zam Öncesi Brüt Ücret (₺)])+UcretAnomaliZEsik*IFERROR(_xlfn.STDEV.P(tblCalisan[Zam Öncesi Brüt Ücret (₺)]),0),0)),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="B21" s="28" t="n">
         <f aca="false">IFERROR(IF(COUNTA(tblCalisan[Çalışan Adı])=0,0,AnomaliCalisanAdedi/COUNTA(tblCalisan[Çalışan Adı])),0)</f>
-        <v>0</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="B22" s="27" t="n">
         <f aca="false">IFERROR(AVERAGE(tblCalisan[Zam Öncesi Brüt Ücret (₺)]),0)</f>
-        <v>20833.3333333333</v>
+        <v>22571.4285714286</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="25" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="B25" s="26" t="n">
         <f aca="false">IFERROR(AVERAGE(tblCalisan[Dönem Günü]),0)</f>
-        <v>2623</v>
+        <v>2525.35714285714</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="25" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="B26" s="27" t="n">
         <f aca="false">IFERROR(SLOPE(tblCalisan[Zam Öncesi Brüt Ücret (₺)],tblCalisan[Dönem Günü]),0)</f>
-        <v>9.12362634055921</v>
+        <v>9.35022450304231</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="25" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="B27" s="28" t="n">
         <f aca="false">IFERROR(IF(SUM(tblCalisan[Zam Öncesi Brüt Ücret (₺)])=0,0,MAX(tblCalisan[Zam Öncesi Brüt Ücret (₺)])/SUM(tblCalisan[Zam Öncesi Brüt Ücret (₺)])),0)</f>
-        <v>0.28</v>
+        <v>0.142405063291139</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="25" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="B28" s="27" t="n">
         <f aca="false">IFERROR(AylikIscilikYuku-ZamOncesiIsverenMaliyeti,0)</f>
-        <v>-103925</v>
+        <v>-288470</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="25" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="B29" s="28" t="n">
         <f aca="false">IFERROR(AVERAGE(tblUrun[İşçilik Oranı]),0)</f>
-        <v>0.262896825396825</v>
+        <v>0.391919870978695</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="25" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="B30" s="28" t="n">
         <f aca="false">IFERROR(IF(COUNTA(tblCalisan[Çalışan Adı])=0,0,AnomaliCalisanAdedi/COUNTA(tblCalisan[Çalışan Adı])),0)</f>
-        <v>0</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="25" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="B31" s="27" t="n">
         <f aca="false">IFERROR(MAX(ABS(SenaryoMaliyetKotumser-SenaryoMaliyetIyimser),ABS(SenaryoYansitmaKotumser-SenaryoYansitmaIyimser)),0)</f>
-        <v>1937.95</v>
+        <v>9878.4</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="25" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="B32" s="27" t="n">
         <f aca="false">IFERROR(SenaryoMaliyetKotumser-SenaryoMaliyetBaz,0)</f>
-        <v>968.975</v>
+        <v>4939.2</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="25" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="B33" s="28" t="n">
         <f aca="false">IFERROR(ToplamMaliyetArtis/MAX(BolumPaydaTaban,ToplamAylikSatisHasilati),0)</f>
-        <v>0.0509682706386741</v>
+        <v>0.135326224747753</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="25" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="B34" s="26" t="n">
         <f aca="false">IFERROR(IF(SUM(tblCalisan[Zam Öncesi Brüt Ücret (₺)])=0,0,SUMPRODUCT(tblCalisan[Zam Öncesi Brüt Ücret (₺)],tblCalisan[Zam Öncesi Brüt Ücret (₺)])/MAX(BolumPaydaTaban,SUM(tblCalisan[Zam Öncesi Brüt Ücret (₺)])^2)),0)</f>
-        <v>0.188352</v>
+        <v>0.0870653741387598</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="25" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="B35" s="26" t="n">
         <f aca="false">VeriKaliteSkoru</f>
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="25" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B36" s="27" t="n">
         <f aca="false">IFERROR(_xlfn.FORECAST.LINEAR(COUNTA(tblCalisan[Dönem Günü])+1,tblCalisan[Zam Öncesi Brüt Ücret (₺)],tblCalisan[Dönem Günü]),0)</f>
-        <v>-3034.07317356957</v>
+        <v>-900.974297101578</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="25" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="B37" s="27" t="n">
         <f aca="false">IFERROR(_xlfn.PERCENTILE.INC(tblCalisan[Zam Sonrası İşveren Maliyeti (₺)],P90Kuantil),0)</f>
-        <v>41496.875</v>
+        <v>55951.875</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="25" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="B38" s="27" t="n">
         <f aca="false">IFERROR(NPV(IskontoOrani,ToplamMaliyetArtis),0)</f>
-        <v>8808.86363636364</v>
+        <v>44901.8181818182</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="25" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="B39" s="27" t="n">
         <f aca="false">IFERROR(MAX(0,ToplamMaliyetArtis-FiyatYansitmaKazanci),0)</f>
-        <v>6576.37400000001</v>
+        <v>36807.3113924051</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="25" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="B40" s="27" t="n">
         <f aca="false">IFERROR(AVERAGE(tblCalisan[Maliyet Farkı (₺)]),0)</f>
-        <v>1614.95833333333</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="25" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="B42" s="26" t="n">
         <f aca="false">modulT1KidemOrt</f>
-        <v>2623</v>
+        <v>2525.35714285714</v>
       </c>
       <c r="C42" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"T1: Ortalama kıdem "&amp;modulT1KidemOrt&amp;" gün",IF(modulT1KidemOrt&gt;KidemSinirGun,"kıdem "&amp;KidemSinirGun/365&amp;" yıl üzerinde, kıdem tazminatı yükü yüksek","kıdem dağılımı normal"))</f>
-        <v>T1: Ortalama kıdem 2623 gün | kıdem 4,93150684931507 yıl üzerinde, kıdem tazminatı yükü yüksek</v>
+        <v>T1: Ortalama kıdem 2525,35714285714 gün | kıdem 4,93150684931507 yıl üzerinde, kıdem tazminatı yükü yüksek</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="25" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="B43" s="27" t="n">
         <f aca="false">modulT2UcretEgim</f>
-        <v>9.12362634055921</v>
+        <v>9.35022450304231</v>
       </c>
       <c r="C43" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"T2: Ücret eğimi "&amp;TEXT(modulT2UcretEgim,"#,##0")&amp;" ₺/gün",IF(modulT2UcretEgim&gt;0,"ücret kıdemle artıyor","ücret kıdemden bağımsız"))</f>
@@ -33357,189 +36007,189 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="25" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="B44" s="28" t="n">
         <f aca="false">modulT3MaliyetParetoPay</f>
-        <v>0.28</v>
+        <v>0.142405063291139</v>
       </c>
       <c r="C44" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"T3: En yüksek ücretli çalışan toplamın %"&amp;TEXT(modulT3MaliyetParetoPay*100,"0")&amp;"",IF(modulT3MaliyetParetoPay&gt;ParetoEsikOran,"yoğunlaşma yüksek, tek çalışana bağımlılık var","dağılım dengeli"))</f>
-        <v>T3: En yüksek ücretli çalışan toplamın %28 | dağılım dengeli</v>
+        <v>T3: En yüksek ücretli çalışan toplamın %14 | dağılım dengeli</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="25" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="B45" s="27" t="n">
         <f aca="false">modulT4DonemFark</f>
-        <v>1614.95833333333</v>
+        <v>3528</v>
       </c>
       <c r="C45" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"T4: Çalışan başına dönem maliyet farkı "&amp;TEXT(modulT4DonemFark,"#,##0")&amp;" ₺",IF(ABS(modulT4DonemFark)&gt;ZamOncesiIsverenMaliyeti*MaliyetArtisEsik,"dönem farkı yüksek, zam etkisi güçlü","dönem farkı makul"))</f>
-        <v>T4: Çalışan başına dönem maliyet farkı 1.615 ₺ | dönem farkı makul</v>
+        <v>T4: Çalışan başına dönem maliyet farkı 3.528 ₺ | dönem farkı makul</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="25" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="B46" s="27" t="n">
         <f aca="false">modulT5MutabakatFark</f>
-        <v>-103925</v>
+        <v>-288470</v>
       </c>
       <c r="C46" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"T5: Ürün işçilik yükü ile fiili maliyet farkı "&amp;TEXT(modulT5MutabakatFark,"#,##0")&amp;" ₺",IF(ABS(modulT5MutabakatFark)&gt;ZamOncesiIsverenMaliyeti*MaliyetArtisEsik,"mutabakat farkı yüksek, maliyet dağılımını denetleyin","mutabakat tutarlı"))</f>
-        <v>T5: Ürün işçilik yükü ile fiili maliyet farkı -103.925 ₺ | mutabakat farkı yüksek, maliyet dağılımını denetleyin</v>
+        <v>T5: Ürün işçilik yükü ile fiili maliyet farkı -288.470 ₺ | mutabakat farkı yüksek, maliyet dağılımını denetleyin</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="25" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="B47" s="28" t="n">
         <f aca="false">modulT6BasabasUcretYuku</f>
-        <v>0.262896825396825</v>
+        <v>0.391919870978695</v>
       </c>
       <c r="C47" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"T6: Ortalama işçilik oranı %"&amp;TEXT(modulT6BasabasUcretYuku*100,"0")&amp;"",IF(modulT6BasabasUcretYuku&gt;FiyatYansitmaEsik,"işçilik yoğun işletme, yansıtma kritik","işçilik oranı düşük"))</f>
-        <v>T6: Ortalama işçilik oranı %26 | işçilik yoğun işletme, yansıtma kritik</v>
+        <v>T6: Ortalama işçilik oranı %39 | işçilik yoğun işletme, yansıtma kritik</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="25" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="B48" s="28" t="n">
         <f aca="false">modulO1AnomaliOran</f>
-        <v>0</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="C48" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"O1: Uç ücretli çalışan oranı %"&amp;TEXT(modulO1AnomaliOran*100,"0.0")&amp;"",IF(modulO1AnomaliOran&gt;0,"anomali çalışanlar tespit edildi, ücretleri denetleyin","anomali yok"))</f>
-        <v>O1: Uç ücretli çalışan oranı %00 | anomali yok</v>
+        <v>O1: Uç ücretli çalışan oranı %07 | anomali çalışanlar tespit edildi, ücretleri denetleyin</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="25" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="B49" s="27" t="n">
         <f aca="false">modulO2TornadoZirve</f>
-        <v>1937.95</v>
+        <v>9878.4</v>
       </c>
       <c r="C49" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"O2: Tornado zirve etki "&amp;TEXT(modulO2TornadoZirve,"#,##0")&amp;" ₺",IF(modulO2TornadoZirve&gt;ToplamMaliyetArtis*ButceEtkiEsikOran,"maliyet duyarlılığı yüksek, zam senaryosu kritik","duyarlılık düşük"))</f>
-        <v>O2: Tornado zirve etki 1.938 ₺ | maliyet duyarlılığı yüksek, zam senaryosu kritik</v>
+        <v>O2: Tornado zirve etki 9.878 ₺ | maliyet duyarlılığı yüksek, zam senaryosu kritik</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="25" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="B50" s="27" t="n">
         <f aca="false">modulO3SenaryoBazFark</f>
-        <v>968.975</v>
+        <v>4939.2</v>
       </c>
       <c r="C50" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"O3: Kötümser-baz fark "&amp;TEXT(modulO3SenaryoBazFark,"#,##0")&amp;" ₺",IF(modulO3SenaryoBazFark&gt;ToplamMaliyetArtis*ButceEtkiEsikOran,"kötümser senaryoda maliyet yükseliyor","senaryo aralığı kabul edilebilir"))</f>
-        <v>O3: Kötümser-baz fark 969 ₺ | senaryo aralığı kabul edilebilir</v>
+        <v>O3: Kötümser-baz fark 4.939 ₺ | senaryo aralığı kabul edilebilir</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="25" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="B51" s="28" t="n">
         <f aca="false">modulO4NakitEtkiOran</f>
-        <v>0.0509682706386741</v>
+        <v>0.135326224747753</v>
       </c>
       <c r="C51" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"O4: Maliyet artışının aylık hasılata oranı %"&amp;TEXT(modulO4NakitEtkiOran*100,"0.0")&amp;"",IF(modulO4NakitEtkiOran&gt;FiyatYansitmaEsik,"nakit etkisi yüksek, fiyat güncellemesi acil","nakit etkisi yönetilebilir"))</f>
-        <v>O4: Maliyet artışının aylık hasılata oranı %05 | nakit etkisi yönetilebilir</v>
+        <v>O4: Maliyet artışının aylık hasılata oranı %14 | nakit etkisi yönetilebilir</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="25" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="B52" s="26" t="n">
         <f aca="false">modulO6MaliyetHhi</f>
-        <v>0.188352</v>
+        <v>0.0870653741387598</v>
       </c>
       <c r="C52" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"O6: Ücret yoğunlaşma endeksi "&amp;TEXT(modulO6MaliyetHhi,"0.00")&amp;"",IF(modulO6MaliyetHhi&gt;HhiYuksekEsik,"yoğunlaşma yüksek","dağılım dengeli"))</f>
-        <v>O6: Ücret yoğunlaşma endeksi 0,19 | dağılım dengeli</v>
+        <v>O6: Ücret yoğunlaşma endeksi 0,09 | dağılım dengeli</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="25" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B53" s="26" t="n">
         <f aca="false">modulO8KaliteSkoru</f>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C53" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"O8: Veri kalite skoru "&amp;TEXT(modulO8KaliteSkoru,"0")&amp;"/100",IF(modulO8KaliteSkoru&gt;=VeriKaliteIyiEsik,"girdi kalitesi iyi","kalite düşük, girişleri tamamlayın"))</f>
-        <v>O8: Veri kalite skoru 70/100 | kalite düşük, girişleri tamamlayın</v>
+        <v>O8: Veri kalite skoru 60/100 | kalite düşük, girişleri tamamlayın</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="25" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="B54" s="27" t="n">
         <f aca="false">modulI1MaliyetTahminOrta</f>
-        <v>-3034.07317356957</v>
+        <v>-900.974297101578</v>
       </c>
       <c r="C54" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"I1: Sonraki kıdem adımında beklenen brüt ücret "&amp;TEXT(modulI1MaliyetTahminOrta,"#,##0")&amp;" ₺",IF(modulI1MaliyetTahminOrta&gt;AsgariUcretYeni,"tahmin asgari ücretin üzerinde","tahmin sınır içinde"))</f>
-        <v>I1: Sonraki kıdem adımında beklenen brüt ücret -3.034 ₺ | tahmin sınır içinde</v>
+        <v>I1: Sonraki kıdem adımında beklenen brüt ücret -901 ₺ | tahmin sınır içinde</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="25" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="B55" s="27" t="n">
         <f aca="false">modulI2MaliyetP90</f>
-        <v>41496.875</v>
+        <v>55951.875</v>
       </c>
       <c r="C55" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"I2: İşveren maliyeti P90 değeri "&amp;TEXT(modulI2MaliyetP90,"#,##0")&amp;" ₺",IF(modulI2MaliyetP90&gt;ZamOncesiIsverenMaliyeti*2,"P90 maliyeti ortalamanın iki katı üzerinde","P90 dağılımı kabul edilebilir"))</f>
-        <v>I2: İşveren maliyeti P90 değeri 41.497 ₺ | P90 dağılımı kabul edilebilir</v>
+        <v>I2: İşveren maliyeti P90 değeri 55.952 ₺ | P90 dağılımı kabul edilebilir</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="25" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="B56" s="27" t="n">
         <f aca="false">modulI3MaliyetNpv</f>
-        <v>8808.86363636364</v>
+        <v>44901.8181818182</v>
       </c>
       <c r="C56" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"I3: Maliyet artışının NPV değeri "&amp;TEXT(modulI3MaliyetNpv,"#,##0")&amp;" ₺",IF(modulI3MaliyetNpv&gt;ToplamMaliyetArtis*NpvEsikOran,"NPV maliyeti yüksek","NPV maliyeti kabul edilebilir"))</f>
-        <v>I3: Maliyet artışının NPV değeri 8.809 ₺ | NPV maliyeti yüksek</v>
+        <v>I3: Maliyet artışının NPV değeri 44.902 ₺ | NPV maliyeti yüksek</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="25" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="B57" s="27" t="n">
         <f aca="false">modulI7AcikKopru</f>
-        <v>6576.37400000001</v>
+        <v>36807.3113924051</v>
       </c>
       <c r="C57" s="29" t="str">
         <f aca="false">_xlfn.TEXTJOIN(" | ",TRUE(),"I7: Yansıtma açık köprüsü "&amp;TEXT(modulI7AcikKopru,"#,##0")&amp;" ₺",IF(modulI7AcikKopru&gt;0,"fiyat yansıtması artışı karşılamıyor, fiyat güncellemesi gerekli","yansıtma artışı karşılıyor"))</f>
-        <v>I7: Yansıtma açık köprüsü 6.576 ₺ | fiyat yansıtması artışı karşılamıyor, fiyat güncellemesi gerekli</v>
+        <v>I7: Yansıtma açık köprüsü 36.807 ₺ | fiyat yansıtması artışı karşılamıyor, fiyat güncellemesi gerekli</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="B58" s="11"/>
       <c r="C58" s="11"/>
@@ -33641,7 +36291,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -33675,32 +36325,32 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="B5" s="30" t="n">
         <f aca="false">IFERROR(COUNTA(tblCalisan[Çalışan Adı]),0)</f>
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="B6" s="30" t="n">
         <f aca="false">IFERROR(COUNTA(tblUrun[Ürün/Hizmet Adı]),0)</f>
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="B7" s="30" t="str">
         <f aca="false">IF(COUNTIF(tblCalisan[Zam Öncesi Brüt Ücret (₺)],"&lt;0")&gt;0,"FAIL","PASS")</f>
@@ -33709,7 +36359,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="B8" s="30" t="str">
         <f aca="false">IF(COUNTIF(tblUrun[Birim Satış Fiyatı (₺)],"&lt;0")&gt;0,"FAIL","PASS")</f>
@@ -33718,7 +36368,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="B9" s="30" t="str">
         <f aca="false">IF(COUNTIF(tblUrun[Birim Satış Fiyatı (₺)],"=0")&gt;0,"WARN","PASS")</f>
@@ -33727,16 +36377,16 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="B10" s="30" t="str">
         <f aca="false">IF(SUMPRODUCT(--(tblUrun[Birim Başına İşçilik (₺)]&gt;tblUrun[Birim Satış Fiyatı (₺)]))&gt;0,"WARN","PASS")</f>
-        <v>PASS</v>
+        <v>WARN</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="B11" s="30" t="str">
         <f aca="false">IF(COUNTIF(tblCalisan[Zam Öncesi Brüt Ücret (₺)],"")&gt;0,"FAIL","PASS")</f>
@@ -33745,7 +36395,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="B12" s="30" t="str">
         <f aca="false">IF(COUNTIF(tblCalisan[İşe Giriş Tarihi],"")&gt;0,"WARN","PASS")</f>
@@ -33754,21 +36404,21 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="B16" s="32" t="n">
         <f aca="false">COUNTIF(B5:B12,"PASS")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="B17" s="32" t="n">
         <f aca="false">COUNTIF(B5:B12,"FAIL")</f>
@@ -33777,43 +36427,43 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="B18" s="32" t="n">
         <f aca="false">COUNTIF(B5:B12,"WARN")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="B19" s="26" t="n">
         <f aca="false">IFERROR(IF(DoluGirisHucre=0,0,MAX(0,VeriKaliteTaban-FAIL_Sayisi*VeriKaliteFailCeza-WARN_Sayisi*VeriKaliteUyariCeza)),0)</f>
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="B20" s="30" t="str">
         <f aca="false">IF(VeriKaliteSkoru&gt;=VeriKaliteIyiEsik,"İYİ",IF(VeriKaliteSkoru&gt;=VeriKaliteOrtaEsik,"ORTA","DÜŞÜK"))</f>
-        <v>ORTA</v>
+        <v>DÜŞÜK</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="31" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="B21" s="32" t="n">
         <f aca="false">IFERROR(COUNTA(tblCalisan[Çalışan Adı])+COUNTA(tblUrun[Ürün/Hizmet Adı]),0)</f>
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="31" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="B22" s="32" t="n">
         <f aca="false">IFERROR(ROWS(tblCalisan)+ROWS(tblUrun),0)</f>
@@ -33822,16 +36472,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="31" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="B23" s="33" t="n">
         <f aca="false">IFERROR(DoluGirisHucre/KayitKapasite,0)</f>
-        <v>0.00333333333333333</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="25" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="B24" s="31" t="str">
         <f aca="false">IF(FAIL_Sayisi=0,"SAĞLIKLI","İNCELE")</f>
@@ -33840,7 +36490,7 @@
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -33944,7 +36594,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -33978,21 +36628,21 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="31" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="B6" s="27" t="n">
         <f aca="false">ToplamMaliyetArtis</f>
-        <v>9689.75</v>
+        <v>49392</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34001,30 +36651,30 @@
       </c>
       <c r="B7" s="28" t="n">
         <f aca="false">MaliyetArtisOrani</f>
-        <v>0.06328</v>
+        <v>0.127594936708861</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="B8" s="28" t="n">
         <f aca="false">FiyatYansitmaOrani</f>
-        <v>0.0166821481481481</v>
+        <v>0.0423679649176635</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="B9" s="27" t="n">
         <f aca="false">modulI7AcikKopru</f>
-        <v>6576.37400000001</v>
+        <v>36807.3113924051</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="B11" s="34" t="str">
         <f aca="false">IF(VeriKaliteSkoru=0,"VERİ YOK",IF(OR(MaliyetArtisOrani&lt;0,modulI7AcikKopru&lt;0),"DURDUR",IF(MaliyetArtisOrani&gt;FiyatYansitmaEsik,"DURDUR",IF(OR(MaliyetArtisOrani&gt;MaliyetArtisEsik,modulI7AcikKopru&gt;0,ABS(modulT5MutabakatFark)&gt;ZamOncesiIsverenMaliyeti*MaliyetArtisEsik,AnomaliCalisanAdedi&gt;0),"İNCELE","UYGUN"))))</f>
@@ -34033,22 +36683,22 @@
     </row>
     <row r="12" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="31" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="B12" s="35" t="str">
         <f aca="false">IF(VeriKaliteSkoru=0,"Girdi eksik; lütfen sarı hücreleri doldurun.",IF(MaliyetArtisOrani&lt;0,"Maliyet artışı negatif: ücret ve fiyat girişlerini kontrol edin.",IF(MaliyetArtisOrani&gt;FiyatYansitmaEsik,"Maliyet artışı %"&amp;TEXT(MaliyetArtisOrani,"0.0%")&amp;" eşiği aşıyor; fiyat yansıtması zorunlu.",IF(modulI7AcikKopru&gt;0,"Fiyat yansıtması maliyet artışını karşılamıyor; açık "&amp;TEXT(modulI7AcikKopru,"#,##0")&amp;" ₺.",IF(ABS(modulT5MutabakatFark)&gt;ZamOncesiIsverenMaliyeti*MaliyetArtisEsik,"Ürün işçilik yükü ile fiili maliyet farkı yüksek; maliyet dağılımını denetleyin.","Maliyet artışı eşikler içinde; fiyat güncellemesi planlanabilir.")))))</f>
-        <v>Fiyat yansıtması maliyet artışını karşılamıyor; açık 6.576 ₺.</v>
+        <v>Fiyat yansıtması maliyet artışını karşılamıyor; açık 36.807 ₺.</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="36" t="str">
         <f aca="false">IF(OR(KararSonuc="VERİ YOK",KararSonuc="DURDUR"),"Ücret ve fiyat girişlerini tamamlayın; yansıtma açığını kapatmak için fiyat cetvelini gözden geçirin",IF(MaliyetArtisOrani&gt;MaliyetArtisEsik,"Maliyet artışı eşik üstünde; fiyat güncellemesini planlayın","Fiyat güncelleme planını sürdürün"))</f>
-        <v>Fiyat güncelleme planını sürdürün</v>
+        <v>Maliyet artışı eşik üstünde; fiyat güncellemesini planlayın</v>
       </c>
       <c r="B15" s="36"/>
       <c r="C15" s="36"/>
@@ -34056,7 +36706,7 @@
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="36" t="str">
         <f aca="false">IF(modulI7AcikKopru&gt;0,"Yansıtma açığı "&amp;TEXT(modulI7AcikKopru,"#,##0")&amp;" ₺; işçilik oranı yüksek ürünlerde fiyatı öncelikle artırın","Fiyat yansıtması artışı karşılıyor")</f>
-        <v>Yansıtma açığı 6.576 ₺; işçilik oranı yüksek ürünlerde fiyatı öncelikle artırın</v>
+        <v>Yansıtma açığı 36.807 ₺; işçilik oranı yüksek ürünlerde fiyatı öncelikle artırın</v>
       </c>
       <c r="B16" s="36"/>
       <c r="C16" s="36"/>
@@ -34064,7 +36714,7 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="36" t="str">
         <f aca="false">IF(AnomaliCalisanAdedi&gt;0,"Uç ücretli çalışanların ücret ve kıdem kayıtlarını inceleyin","Ücret dağılımı tutarlı")</f>
-        <v>Ücret dağılımı tutarlı</v>
+        <v>Uç ücretli çalışanların ücret ve kıdem kayıtlarını inceleyin</v>
       </c>
       <c r="B17" s="36"/>
       <c r="C17" s="36"/>
@@ -34079,7 +36729,7 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -34184,7 +36834,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -34218,41 +36868,41 @@
     </row>
     <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="37" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="38" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="B5" s="38"/>
       <c r="D5" s="39" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="E5" s="39"/>
       <c r="G5" s="40" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="H5" s="40"/>
       <c r="J5" s="41" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="K5" s="41"/>
     </row>
     <row r="6" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="42" t="n">
         <f aca="false">ToplamMaliyetArtis</f>
-        <v>9689.75</v>
+        <v>49392</v>
       </c>
       <c r="B6" s="42"/>
       <c r="D6" s="43" t="n">
         <f aca="false">MaliyetArtisOrani</f>
-        <v>0.06328</v>
+        <v>0.127594936708861</v>
       </c>
       <c r="E6" s="43"/>
       <c r="G6" s="43" t="n">
         <f aca="false">FiyatYansitmaOrani</f>
-        <v>0.0166821481481481</v>
+        <v>0.0423679649176635</v>
       </c>
       <c r="H6" s="43"/>
       <c r="J6" s="44" t="str">
@@ -34263,43 +36913,43 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="45" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="B8" s="27" t="n">
         <f aca="false">ZamOncesiIsverenMaliyeti</f>
-        <v>153125</v>
+        <v>387100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="45" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="B9" s="27" t="n">
         <f aca="false">ZamSonrasiIsverenMaliyeti</f>
-        <v>162814.75</v>
+        <v>436492</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="45" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="B10" s="27" t="n">
         <f aca="false">FiyatYansitmaKazanci</f>
-        <v>3113.37599999999</v>
+        <v>12584.6886075949</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="45" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B11" s="26" t="n">
         <f aca="false">ToplamCalisanSayisi</f>
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="45" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="B12" s="28" t="n">
         <f aca="false">AsgariUcretZamOrani</f>
@@ -34308,32 +36958,32 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="45" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="B13" s="26" t="n">
         <f aca="false">VeriKaliteSkoru</f>
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="45" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="B14" s="27" t="n">
         <f aca="false">modulI7AcikKopru</f>
-        <v>6576.37400000001</v>
+        <v>36807.3113924051</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="46" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="B16" s="46"/>
       <c r="C16" s="46"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="B17" s="45" t="str">
         <f aca="false">KararSonuc</f>
@@ -34343,14 +36993,14 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="str">
         <f aca="false">KararGerekce</f>
-        <v>Fiyat yansıtması maliyet artışını karşılamıyor; açık 6.576 ₺.</v>
+        <v>Fiyat yansıtması maliyet artışını karşılamıyor; açık 36.807 ₺.</v>
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="46" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="B19" s="46"/>
       <c r="C19" s="46"/>
@@ -34358,14 +37008,14 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="36" t="str">
         <f aca="false">IF(VeriKaliteSkoru=0,"Veri yok","1. Maliyet artışı %"&amp;TEXT(MaliyetArtisOrani*100,"0.0")&amp;" — fiyat yansıtma oranı %"&amp;TEXT(FiyatYansitmaOrani*100,"0.0")&amp;"")</f>
-        <v>1. Maliyet artışı %06 — fiyat yansıtma oranı %02</v>
+        <v>1. Maliyet artışı %13 — fiyat yansıtma oranı %04</v>
       </c>
       <c r="B20" s="36"/>
       <c r="C20" s="36"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="36" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="B21" s="36"/>
       <c r="C21" s="36"/>
@@ -34373,69 +37023,69 @@
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="36" t="str">
         <f aca="false">IF(VeriKaliteSkoru=0,"Veri yok","3. Veri kalitesi "&amp;VeriKaliteSkoru&amp;" puan; düşükse karar güveni sınırlıdır.")</f>
-        <v>3. Veri kalitesi 70 puan; düşükse karar güveni sınırlıdır.</v>
+        <v>3. Veri kalitesi 60 puan; düşükse karar güveni sınırlıdır.</v>
       </c>
       <c r="B22" s="36"/>
       <c r="C22" s="36"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="45" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="B25" s="47" t="n">
         <f aca="false">ZamOncesiIsverenMaliyeti</f>
-        <v>153125</v>
+        <v>387100</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="B26" s="47" t="n">
         <f aca="false">ZamSonrasiIsverenMaliyeti</f>
-        <v>162814.75</v>
+        <v>436492</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="B27" s="47" t="n">
         <f aca="false">FiyatYansitmaKazanci</f>
-        <v>3113.37599999999</v>
+        <v>12584.6886075949</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="45" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="B30" s="33" t="n">
         <f aca="false">IFERROR(MIN(1,FiyatYansitmaOrani/MAX(MaliyetArtisOrani,BolumPaydaTaban)),0)</f>
-        <v>0.263624338624339</v>
+        <v>0.332050518699942</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="31" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="B31" s="33" t="n">
         <f aca="false">IFERROR(MAX(0,1-MIN(1,FiyatYansitmaOrani/MAX(MaliyetArtisOrani,BolumPaydaTaban))),0)</f>
-        <v>0.736375661375661</v>
+        <v>0.667949481300058</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="45" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34445,7 +37095,7 @@
       </c>
       <c r="B34" s="48" t="n">
         <f aca="false">IFERROR(INDEX(tblUrun[Fiyat Yansıtma Oranı],ROW()-ROW($A$33)),0)</f>
-        <v>0.01582</v>
+        <v>0.0318987341772152</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34455,7 +37105,7 @@
       </c>
       <c r="B35" s="48" t="n">
         <f aca="false">IFERROR(INDEX(tblUrun[Fiyat Yansıtma Oranı],ROW()-ROW($A$33)),0)</f>
-        <v>0.0175777777777778</v>
+        <v>0.0354430379746835</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34465,7 +37115,7 @@
       </c>
       <c r="B36" s="48" t="n">
         <f aca="false">IFERROR(INDEX(tblUrun[Fiyat Yansıtma Oranı],ROW()-ROW($A$33)),0)</f>
-        <v>0.0168746666666667</v>
+        <v>0.0340253164556962</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34475,44 +37125,44 @@
       </c>
       <c r="B37" s="48" t="n">
         <f aca="false">IFERROR(INDEX(tblUrun[Fiyat Yansıtma Oranı],ROW()-ROW($A$33)),0)</f>
-        <v>0.016272</v>
+        <v>0.0328101265822785</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="45" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="31" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="B40" s="47" t="n">
         <f aca="false">ToplamMaliyetArtis</f>
-        <v>9689.75</v>
+        <v>49392</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="B41" s="47" t="n">
         <f aca="false">FiyatYansitmaKazanci</f>
-        <v>3113.37599999999</v>
+        <v>12584.6886075949</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="31" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="B42" s="47" t="n">
         <f aca="false">modulI7AcikKopru</f>
-        <v>6576.37400000001</v>
+        <v>36807.3113924051</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="45" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34557,30 +37207,30 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="45" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="31" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="B51" s="47" t="n">
         <f aca="false">modulI1MaliyetTahminOrta</f>
-        <v>-3034.07317356957</v>
+        <v>-900.974297101578</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="31" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="B52" s="47" t="n">
         <f aca="false">modulI2MaliyetP90</f>
-        <v>41496.875</v>
+        <v>55951.875</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="B54" s="11"/>
       <c r="C54" s="11"/>
@@ -34700,7 +37350,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -34734,94 +37384,94 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="B7" s="27" t="n">
         <f aca="false">IFERROR(ToplamMaliyetArtis*(1+SenaryoKotumserKat),0)</f>
-        <v>10658.725</v>
+        <v>54331.2</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">ToplamMaliyetArtis</f>
-        <v>9689.75</v>
+        <v>49392</v>
       </c>
       <c r="D7" s="27" t="n">
         <f aca="false">IFERROR(ToplamMaliyetArtis*(1-SenaryoIyimserKat),0)</f>
-        <v>8720.775</v>
+        <v>44452.8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="B8" s="28" t="n">
         <f aca="false">IFERROR(FiyatYansitmaOrani*(1-SenaryoKotumserKat),0)</f>
-        <v>0.0150139333333333</v>
+        <v>0.0381311684258972</v>
       </c>
       <c r="C8" s="28" t="n">
         <f aca="false">FiyatYansitmaOrani</f>
-        <v>0.0166821481481481</v>
+        <v>0.0423679649176635</v>
       </c>
       <c r="D8" s="28" t="n">
         <f aca="false">IFERROR(FiyatYansitmaOrani*(1+SenaryoIyimserKat),0)</f>
-        <v>0.018350362962963</v>
+        <v>0.0466047614094299</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="B9" s="27" t="n">
         <f aca="false">IFERROR(FiyatYansitmaKazanci*(1-SenaryoKotumserKat),0)</f>
-        <v>2802.03839999999</v>
+        <v>11326.2197468354</v>
       </c>
       <c r="C9" s="27" t="n">
         <f aca="false">FiyatYansitmaKazanci</f>
-        <v>3113.37599999999</v>
+        <v>12584.6886075949</v>
       </c>
       <c r="D9" s="27" t="n">
         <f aca="false">IFERROR(FiyatYansitmaKazanci*(1+SenaryoIyimserKat),0)</f>
-        <v>3424.71359999999</v>
+        <v>13843.1574683544</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="B10" s="27" t="n">
         <f aca="false">IFERROR(MAX(0,B7-B9),0)</f>
-        <v>7856.68660000001</v>
+        <v>43004.9802531646</v>
       </c>
       <c r="C10" s="27" t="n">
         <f aca="false">IFERROR(MAX(0,C7-C9),0)</f>
-        <v>6576.37400000001</v>
+        <v>36807.3113924051</v>
       </c>
       <c r="D10" s="27" t="n">
         <f aca="false">IFERROR(MAX(0,D7-D9),0)</f>
-        <v>5296.06140000001</v>
+        <v>30609.6425316456</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="B11" s="30" t="str">
         <f aca="false">IF(VeriKaliteSkoru=0,"VERİ YOK",IF(B7&gt;FiyatYansitmaEsik*ZamOncesiIsverenMaliyeti,"DURDUR",IF(OR(B10&gt;0,B7&gt;MaliyetArtisEsik*ZamOncesiIsverenMaliyeti),"İNCELE","UYGUN")))</f>
@@ -34838,12 +37488,12 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="24" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="31" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="B14" s="33" t="n">
         <f aca="false">IFERROR(AsgariUcretZamOrani*(1-DuyarliDegisim),0)</f>
@@ -34860,24 +37510,24 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="31" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="B15" s="47" t="n">
         <f aca="false">IFERROR(MAX(0,AsgariUcretZamOrani*(1-DuyarliDegisim)*ZamOncesiIsverenMaliyeti),0)</f>
-        <v>36367.1875</v>
+        <v>91936.25</v>
       </c>
       <c r="C15" s="47" t="n">
         <f aca="false">IFERROR(MAX(0,AsgariUcretZamOrani*ZamOncesiIsverenMaliyeti),0)</f>
-        <v>38281.25</v>
+        <v>96775</v>
       </c>
       <c r="D15" s="47" t="n">
         <f aca="false">IFERROR(MAX(0,AsgariUcretZamOrani*(1+DuyarliDegisim)*ZamOncesiIsverenMaliyeti),0)</f>
-        <v>40195.3125</v>
+        <v>101613.75</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="B17" s="31" t="str">
         <f aca="false">IF(VeriKaliteSkoru=0,"VERİ YOK",IF(MAX(B10,C10,D10)&gt;0,"YANSITMA AÇIĞI VAR","YANSITMA YETERLİ"))</f>
@@ -34886,7 +37536,7 @@
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
